--- a/artfynd/A 19314-2026 artfynd.xlsx
+++ b/artfynd/A 19314-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>102749629</v>
+        <v>102750103</v>
       </c>
       <c r="B2" t="n">
-        <v>78533</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>229748</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gytterlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Protopannaria pezizoides</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -716,10 +711,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>603194.077368325</v>
+        <v>603181</v>
       </c>
       <c r="R2" t="n">
-        <v>7053973.713716422</v>
+        <v>7053949</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -749,19 +744,9 @@
           <t>2022-08-08</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-08-08</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,12 +776,7 @@
         <v>102750352</v>
       </c>
       <c r="B3" t="n">
-        <v>98493</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101299</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -830,10 +810,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>603149.6310751486</v>
+        <v>603149</v>
       </c>
       <c r="R3" t="n">
-        <v>7054023.931227425</v>
+        <v>7054024</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -863,19 +843,9 @@
           <t>2022-08-08</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-08-08</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,51 +872,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>102750904</v>
+        <v>122246470</v>
       </c>
       <c r="B4" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101299</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>1365</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lappranunkel</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Coptidium lapponicum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Tzvelev</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sollefteå, Ång</t>
+          <t>Bysjöns SV strand, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>603151.5257414198</v>
+        <v>603150</v>
       </c>
       <c r="R4" t="n">
-        <v>7054034.236325787</v>
+        <v>7054024</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -971,24 +935,19 @@
           <t>Junsele</t>
         </is>
       </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Y-Sol-0076</t>
+        </is>
+      </c>
       <c r="Y4" t="inlineStr">
         <is>
           <t>2022-08-08</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-08-08</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1003,7 +962,7 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Lena Högberg</t>
+          <t>Sofia Lund</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
@@ -1011,55 +970,55 @@
           <t>Lena Högberg</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>102750103</v>
+        <v>102749496</v>
       </c>
       <c r="B5" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96603</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>2166</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skör kvastmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dicranum fragilifolium</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Lindb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>603180.6319031869</v>
+        <v>603212</v>
       </c>
       <c r="R5" t="n">
-        <v>7053948.335096659</v>
+        <v>7053990</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1089,19 +1048,9 @@
           <t>2022-08-08</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-08-08</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,15 +1077,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>102749496</v>
+        <v>102749546</v>
       </c>
       <c r="B6" t="n">
-        <v>93278</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97231</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1144,21 +1088,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2166</v>
+        <v>2869</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skör kvastmossa</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dicranum fragilifolium</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Lindb.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1170,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>603212.2815954251</v>
+        <v>603212</v>
       </c>
       <c r="R6" t="n">
-        <v>7053989.894202431</v>
+        <v>7053990</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1203,19 +1147,9 @@
           <t>2022-08-08</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-08-08</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1242,15 +1176,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>102749546</v>
+        <v>102750364</v>
       </c>
       <c r="B7" t="n">
-        <v>93868</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97231</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1284,10 +1213,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>603212.2815954251</v>
+        <v>603149</v>
       </c>
       <c r="R7" t="n">
-        <v>7053989.894202431</v>
+        <v>7054024</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1317,19 +1246,9 @@
           <t>2022-08-08</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-08-08</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1359,12 +1278,7 @@
         <v>102750114</v>
       </c>
       <c r="B8" t="n">
-        <v>73678</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83290</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1397,10 +1311,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>603162.9906518233</v>
+        <v>603163</v>
       </c>
       <c r="R8" t="n">
-        <v>7053983.391479112</v>
+        <v>7053983</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1430,19 +1344,9 @@
           <t>2022-08-08</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-08-08</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1469,15 +1373,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>102750446</v>
+        <v>102750249</v>
       </c>
       <c r="B9" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1485,21 +1384,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1510,10 +1409,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>603151.5257414198</v>
+        <v>603142</v>
       </c>
       <c r="R9" t="n">
-        <v>7054034.236325787</v>
+        <v>7053956</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1543,19 +1442,9 @@
           <t>2022-08-08</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-08-08</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1582,52 +1471,46 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>102750364</v>
+        <v>102750446</v>
       </c>
       <c r="B10" t="n">
-        <v>93868</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2869</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>603149.6310751486</v>
+        <v>603152</v>
       </c>
       <c r="R10" t="n">
-        <v>7054023.931227425</v>
+        <v>7054034</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1657,19 +1540,9 @@
           <t>2022-08-08</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2022-08-08</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1693,6 +1566,104 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>102749629</v>
+      </c>
+      <c r="B11" t="n">
+        <v>80398</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>229748</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Gytterlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Protopannaria pezizoides</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Weber) P.M.Jørg. &amp; S.Ekman</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>603195</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7053974</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2022-08-08</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2022-08-08</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Lena Högberg</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Lena Högberg</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 19314-2026 artfynd.xlsx
+++ b/artfynd/A 19314-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102750103</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -869,6 +879,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102750352</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122246470</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1074,6 +1094,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102749496</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1173,6 +1198,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102749546</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1272,6 +1302,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102750364</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1370,6 +1405,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102750114</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1468,6 +1508,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102750249</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1566,6 +1611,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102750446</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1664,8 +1714,25 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102749629</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>